--- a/dados/SURVEY_BRAM.xlsx
+++ b/dados/SURVEY_BRAM.xlsx
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S23"/>
+  <dimension ref="A1:S24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="30.109375" customWidth="1" style="8" min="1" max="1"/>
@@ -1153,6 +1153,25 @@
       <c r="S23" t="inlineStr">
         <is>
           <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="n">
+        <v>46279.73333333333</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-22.385187</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-41.767628</v>
+      </c>
+      <c r="Q24" s="12" t="n">
+        <v>46279.73194444444</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>Moored</t>
         </is>
       </c>
     </row>
@@ -1169,7 +1188,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S22"/>
+  <dimension ref="A1:S23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.5546875" customWidth="1" min="1" max="1"/>
@@ -1740,6 +1759,25 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="12" t="n">
+        <v>46279.73333333333</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-23.314625</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-43.106281</v>
+      </c>
+      <c r="Q23" s="12" t="n">
+        <v>46278.16180555556</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:S14"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1752,7 +1790,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S22"/>
+  <dimension ref="A1:S23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.5546875" customWidth="1" min="1" max="1"/>
@@ -2317,6 +2355,25 @@
         <v>46278.86180555556</v>
       </c>
       <c r="S22" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="n">
+        <v>46279.73333333333</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-21.860342</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-41.020283</v>
+      </c>
+      <c r="Q23" s="12" t="n">
+        <v>46279.72847222222</v>
+      </c>
+      <c r="S23" t="inlineStr">
         <is>
           <t>Moored</t>
         </is>
@@ -2334,7 +2391,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S23"/>
+  <dimension ref="A1:S24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="12.6640625" customWidth="1" min="1" max="1"/>
@@ -2980,6 +3037,25 @@
         <v>46278.78333333333</v>
       </c>
       <c r="S23" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="n">
+        <v>46279.73333333333</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-24.178099</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-42.358501</v>
+      </c>
+      <c r="Q24" s="12" t="n">
+        <v>46278.92222222222</v>
+      </c>
+      <c r="S24" t="inlineStr">
         <is>
           <t>Underway using Engine</t>
         </is>
@@ -2997,7 +3073,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S22"/>
+  <dimension ref="A1:S23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="19.5546875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -3568,6 +3644,25 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="12" t="n">
+        <v>46279.73333333333</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-25.030201</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-42.652859</v>
+      </c>
+      <c r="Q23" s="12" t="n">
+        <v>46277.40694444445</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>Restricted Manoeuvrability</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:S15"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3580,7 +3675,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S23"/>
+  <dimension ref="A1:S24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="24.5546875" customWidth="1" min="1" max="1"/>
@@ -4233,6 +4328,25 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="12" t="n">
+        <v>46279.73333333333</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-24.566067</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-42.51263</v>
+      </c>
+      <c r="Q24" s="12" t="n">
+        <v>46278.53611111111</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>Restricted Manoeuvrability</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:S16"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4245,7 +4359,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S22"/>
+  <dimension ref="A1:S23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="27.6640625" customWidth="1" style="8" min="1" max="1"/>
@@ -4872,6 +4986,25 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="12" t="n">
+        <v>46279.73333333333</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-21.881546</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-41.005341</v>
+      </c>
+      <c r="Q23" s="12" t="n">
+        <v>46279.73333333333</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:S15"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4884,7 +5017,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S23"/>
+  <dimension ref="A1:S24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="34.44140625" customWidth="1" style="8" min="1" max="1"/>
@@ -5537,6 +5670,25 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="12" t="n">
+        <v>46279.73333333333</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-22.844061</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-43.143723</v>
+      </c>
+      <c r="Q24" s="12" t="n">
+        <v>46279.73333333333</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:S15"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5549,7 +5701,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S25"/>
+  <dimension ref="A1:S26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="25.33203125" customWidth="1" style="8" min="1" max="1"/>
@@ -6270,6 +6422,25 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="12" t="n">
+        <v>46279.73333333333</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-22.87076</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-43.122875</v>
+      </c>
+      <c r="Q26" s="12" t="n">
+        <v>46279.73263888889</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:S18"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6282,7 +6453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S23"/>
+  <dimension ref="A1:S24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="23.33203125" customWidth="1" style="8" min="1" max="1"/>
@@ -6934,6 +7105,25 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="12" t="n">
+        <v>46279.73333333333</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-23.822506</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-42.883278</v>
+      </c>
+      <c r="Q24" s="12" t="n">
+        <v>46276.55486111111</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:S15"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6946,7 +7136,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S23"/>
+  <dimension ref="A1:S24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="23.6640625" customWidth="1" style="8" min="1" max="1"/>
@@ -7601,6 +7791,25 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="12" t="n">
+        <v>46279.73333333333</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-21.855532</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-40.945045</v>
+      </c>
+      <c r="Q24" s="12" t="n">
+        <v>46279.73263888889</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:S15"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7613,7 +7822,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S23"/>
+  <dimension ref="A1:S24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="39.6640625" customWidth="1" style="8" min="1" max="1"/>
@@ -8265,6 +8474,25 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="12" t="n">
+        <v>46279.73333333333</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-23.310389</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-42.994446</v>
+      </c>
+      <c r="Q24" s="12" t="n">
+        <v>46279.21597222222</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>Underway</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:S15"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8277,7 +8505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S22"/>
+  <dimension ref="A1:S23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="26" customWidth="1" style="8" min="1" max="1"/>
@@ -8842,6 +9070,25 @@
         <v>46278.36527777778</v>
       </c>
       <c r="S22" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="n">
+        <v>46279.73333333333</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-24.776045</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-42.720772</v>
+      </c>
+      <c r="Q23" s="12" t="n">
+        <v>46278.36527777778</v>
+      </c>
+      <c r="S23" t="inlineStr">
         <is>
           <t>Stopped</t>
         </is>
@@ -8859,7 +9106,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S23"/>
+  <dimension ref="A1:S24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="11.33203125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -9513,6 +9760,25 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="12" t="n">
+        <v>46279.73333333333</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-24.53388</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-42.475761</v>
+      </c>
+      <c r="Q24" s="12" t="n">
+        <v>46278.47986111111</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:S15"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/dados/SURVEY_BRAM.xlsx
+++ b/dados/SURVEY_BRAM.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" tabRatio="1000" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="1000" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="BRAM ATLAS" sheetId="1" state="visible" r:id="rId1"/>
@@ -43,10 +43,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -89,7 +88,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -108,7 +107,6 @@
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -506,11 +504,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S24"/>
+  <dimension ref="A1:S49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="30.109375" customWidth="1" style="8" min="1" max="1"/>
-    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="13" max="14"/>
     <col width="20.6640625" customWidth="1" style="8" min="17" max="17"/>
     <col width="33.5546875" customWidth="1" min="19" max="19"/>
   </cols>
@@ -1138,7 +1136,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="n">
+      <c r="A23" s="7" t="n">
         <v>46278.85416666666</v>
       </c>
       <c r="M23" t="n">
@@ -1147,7 +1145,7 @@
       <c r="N23" t="n">
         <v>-41.719658</v>
       </c>
-      <c r="Q23" s="12" t="n">
+      <c r="Q23" s="7" t="n">
         <v>46278.85208333333</v>
       </c>
       <c r="S23" t="inlineStr">
@@ -1157,7 +1155,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="12" t="n">
+      <c r="A24" s="7" t="n">
         <v>46279.73333333333</v>
       </c>
       <c r="M24" t="n">
@@ -1166,12 +1164,531 @@
       <c r="N24" t="n">
         <v>-41.767628</v>
       </c>
-      <c r="Q24" s="12" t="n">
+      <c r="Q24" s="7" t="n">
         <v>46279.73194444444</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
           <t>Moored</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="n">
+        <v>46280.53125</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-22.385178</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-41.767586</v>
+      </c>
+      <c r="Q25" s="7" t="n">
+        <v>46280.52986111111</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="n">
+        <v>46281.53472222222</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-23.96476</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-42.220581</v>
+      </c>
+      <c r="Q26" s="7" t="n">
+        <v>46281.16736111111</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="n">
+        <v>46283.75694444445</v>
+      </c>
+      <c r="M27" t="n">
+        <v>-24.493652</v>
+      </c>
+      <c r="N27" t="n">
+        <v>-42.43528</v>
+      </c>
+      <c r="Q27" s="7" t="n">
+        <v>46282.49375</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>Restricted Manoeuvrability</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="n">
+        <v>46287.35763888889</v>
+      </c>
+      <c r="M28" t="n">
+        <v>-22.845287</v>
+      </c>
+      <c r="N28" t="n">
+        <v>-43.137287</v>
+      </c>
+      <c r="Q28" s="7" t="n">
+        <v>46287.35416666666</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="n">
+        <v>46287.71666666667</v>
+      </c>
+      <c r="M29" t="n">
+        <v>-22.846174</v>
+      </c>
+      <c r="N29" t="n">
+        <v>-43.137779</v>
+      </c>
+      <c r="Q29" s="7" t="n">
+        <v>46287.71527777778</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="n">
+        <v>46288.26597222222</v>
+      </c>
+      <c r="M30" t="n">
+        <v>-24.326523</v>
+      </c>
+      <c r="N30" t="n">
+        <v>-42.603832</v>
+      </c>
+      <c r="Q30" s="7" t="n">
+        <v>46288.29236111111</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="n">
+        <v>46290.46666666667</v>
+      </c>
+      <c r="M31" t="n">
+        <v>-24.326523</v>
+      </c>
+      <c r="N31" t="n">
+        <v>-42.603832</v>
+      </c>
+      <c r="Q31" s="7" t="n">
+        <v>46288.29236111111</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="n">
+        <v>46291.32291666666</v>
+      </c>
+      <c r="M32" t="n">
+        <v>-24.326523</v>
+      </c>
+      <c r="N32" t="n">
+        <v>-42.603832</v>
+      </c>
+      <c r="Q32" s="7" t="n">
+        <v>46288.29236111111</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="n">
+        <v>46295.34652777778</v>
+      </c>
+      <c r="M33" t="n">
+        <v>-24.600296</v>
+      </c>
+      <c r="N33" t="n">
+        <v>-42.49585</v>
+      </c>
+      <c r="Q33" s="7" t="n">
+        <v>46295.275</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>Restricted Manoeuvrability</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="n">
+        <v>46296.35902777778</v>
+      </c>
+      <c r="M34" t="n">
+        <v>-24.598761</v>
+      </c>
+      <c r="N34" t="n">
+        <v>-42.492901</v>
+      </c>
+      <c r="Q34" s="7" t="n">
+        <v>46296.33541666667</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>Restricted Manoeuvrability</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="n">
+        <v>46296.53263888889</v>
+      </c>
+      <c r="M35" t="n">
+        <v>-24.598782</v>
+      </c>
+      <c r="N35" t="n">
+        <v>-42.492855</v>
+      </c>
+      <c r="Q35" s="7" t="n">
+        <v>46296.46736111111</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>Restricted Manoeuvrability</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="n">
+        <v>46297.45625</v>
+      </c>
+      <c r="M36" t="n">
+        <v>-24.599344</v>
+      </c>
+      <c r="N36" t="n">
+        <v>-42.493065</v>
+      </c>
+      <c r="Q36" s="7" t="n">
+        <v>46297.44236111111</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>Restricted Manoeuvrability</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="n">
+        <v>46298.43402777778</v>
+      </c>
+      <c r="M37" t="n">
+        <v>-24.599459</v>
+      </c>
+      <c r="N37" t="n">
+        <v>-42.492931</v>
+      </c>
+      <c r="Q37" s="7" t="n">
+        <v>46297.55069444444</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>Restricted Manoeuvrability</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="n">
+        <v>46298.88194444445</v>
+      </c>
+      <c r="M38" t="n">
+        <v>-24.598989</v>
+      </c>
+      <c r="N38" t="n">
+        <v>-42.494114</v>
+      </c>
+      <c r="Q38" s="7" t="n">
+        <v>46298.65208333333</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>Restricted Manoeuvrability</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-10-05 11:51</t>
+        </is>
+      </c>
+      <c r="M39" t="n">
+        <v>-24.598785</v>
+      </c>
+      <c r="N39" t="n">
+        <v>-42.494213</v>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>2026-10-05 02:01</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>Restricted Manoeuvrability</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:23</t>
+        </is>
+      </c>
+      <c r="M40" t="n">
+        <v>-22.855782</v>
+      </c>
+      <c r="N40" t="n">
+        <v>-43.161346</v>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:17</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-10-08 08:36</t>
+        </is>
+      </c>
+      <c r="M41" t="n">
+        <v>-24.48225</v>
+      </c>
+      <c r="N41" t="n">
+        <v>-42.555992</v>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>2026-10-07 07:35</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-10-12 10:22</t>
+        </is>
+      </c>
+      <c r="M42" t="n">
+        <v>-24.588842</v>
+      </c>
+      <c r="N42" t="n">
+        <v>-42.516613</v>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>2026-10-12 10:09</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-10-12 14:32</t>
+        </is>
+      </c>
+      <c r="M43" t="n">
+        <v>-24.588882</v>
+      </c>
+      <c r="N43" t="n">
+        <v>-42.516674</v>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>2026-10-12 10:37</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-10-13 05:59</t>
+        </is>
+      </c>
+      <c r="M44" t="n">
+        <v>-24.588882</v>
+      </c>
+      <c r="N44" t="n">
+        <v>-42.516674</v>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>2026-10-12 10:37</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-10-14 14:10</t>
+        </is>
+      </c>
+      <c r="M45" t="n">
+        <v>-24.587027</v>
+      </c>
+      <c r="N45" t="n">
+        <v>-42.518066</v>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>2026-10-14 08:39</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-10-15 07:21</t>
+        </is>
+      </c>
+      <c r="M46" t="n">
+        <v>-24.587027</v>
+      </c>
+      <c r="N46" t="n">
+        <v>-42.518066</v>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>2026-10-14 08:39</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-10-18 09:38</t>
+        </is>
+      </c>
+      <c r="M47" t="n">
+        <v>-22.271162</v>
+      </c>
+      <c r="N47" t="n">
+        <v>-39.864014</v>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>2026-10-18 09:22</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-10-18 14:49</t>
+        </is>
+      </c>
+      <c r="M48" t="n">
+        <v>-22.316269</v>
+      </c>
+      <c r="N48" t="n">
+        <v>-39.675007</v>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>2026-10-18 14:20</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:41</t>
+        </is>
+      </c>
+      <c r="M49" t="n">
+        <v>-22.384501</v>
+      </c>
+      <c r="N49" t="n">
+        <v>-41.768784</v>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:39</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>Stopped</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1705,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S23"/>
+  <dimension ref="A1:S47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.5546875" customWidth="1" min="1" max="1"/>
@@ -1741,7 +2258,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="12" t="n">
+      <c r="A22" s="7" t="n">
         <v>46278.85416666666</v>
       </c>
       <c r="M22" t="n">
@@ -1750,7 +2267,7 @@
       <c r="N22" t="n">
         <v>-43.106281</v>
       </c>
-      <c r="Q22" s="12" t="n">
+      <c r="Q22" s="7" t="n">
         <v>46278.16180555556</v>
       </c>
       <c r="S22" t="inlineStr">
@@ -1760,7 +2277,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="n">
+      <c r="A23" s="7" t="n">
         <v>46279.73333333333</v>
       </c>
       <c r="M23" t="n">
@@ -1769,12 +2286,508 @@
       <c r="N23" t="n">
         <v>-43.106281</v>
       </c>
-      <c r="Q23" s="12" t="n">
+      <c r="Q23" s="7" t="n">
         <v>46278.16180555556</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
           <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="n">
+        <v>46280.53125</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-23.314625</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-43.106281</v>
+      </c>
+      <c r="Q24" s="7" t="n">
+        <v>46278.16180555556</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="n">
+        <v>46281.53472222222</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-23.314625</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-43.106281</v>
+      </c>
+      <c r="Q25" s="7" t="n">
+        <v>46278.16180555556</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="n">
+        <v>46283.75694444445</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-22.888908</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-43.214901</v>
+      </c>
+      <c r="Q26" s="7" t="n">
+        <v>46283.75277777778</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="n">
+        <v>46287.35763888889</v>
+      </c>
+      <c r="M27" t="n">
+        <v>-22.855654</v>
+      </c>
+      <c r="N27" t="n">
+        <v>-43.161396</v>
+      </c>
+      <c r="Q27" s="7" t="n">
+        <v>46287.35625</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="n">
+        <v>46287.71666666667</v>
+      </c>
+      <c r="M28" t="n">
+        <v>-22.855839</v>
+      </c>
+      <c r="N28" t="n">
+        <v>-43.161179</v>
+      </c>
+      <c r="Q28" s="7" t="n">
+        <v>46287.71458333333</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="n">
+        <v>46288.26597222222</v>
+      </c>
+      <c r="M29" t="n">
+        <v>-22.855427</v>
+      </c>
+      <c r="N29" t="n">
+        <v>-43.163078</v>
+      </c>
+      <c r="Q29" s="7" t="n">
+        <v>46290.37986111111</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="n">
+        <v>46290.46666666667</v>
+      </c>
+      <c r="M30" t="n">
+        <v>-23.073246</v>
+      </c>
+      <c r="N30" t="n">
+        <v>-43.100281</v>
+      </c>
+      <c r="Q30" s="7" t="n">
+        <v>46290.46666666667</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="n">
+        <v>46291.32291666666</v>
+      </c>
+      <c r="M31" t="n">
+        <v>-23.9634</v>
+      </c>
+      <c r="N31" t="n">
+        <v>-42.907269</v>
+      </c>
+      <c r="Q31" s="7" t="n">
+        <v>46290.6875</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="n">
+        <v>46295.34652777778</v>
+      </c>
+      <c r="M32" t="n">
+        <v>-22.843796</v>
+      </c>
+      <c r="N32" t="n">
+        <v>-43.148228</v>
+      </c>
+      <c r="Q32" s="7" t="n">
+        <v>46295.34652777778</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="n">
+        <v>46296.35902777778</v>
+      </c>
+      <c r="M33" t="n">
+        <v>-22.891048</v>
+      </c>
+      <c r="N33" t="n">
+        <v>-43.21394</v>
+      </c>
+      <c r="Q33" s="7" t="n">
+        <v>46296.35416666666</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="n">
+        <v>46296.53263888889</v>
+      </c>
+      <c r="M34" t="n">
+        <v>-22.89105</v>
+      </c>
+      <c r="N34" t="n">
+        <v>-43.213905</v>
+      </c>
+      <c r="Q34" s="7" t="n">
+        <v>46296.52708333333</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="n">
+        <v>46296.65833333333</v>
+      </c>
+      <c r="M35" t="n">
+        <v>-22.860853</v>
+      </c>
+      <c r="N35" t="n">
+        <v>-43.167175</v>
+      </c>
+      <c r="Q35" s="7" t="n">
+        <v>46296.64861111111</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="n">
+        <v>46297.45625</v>
+      </c>
+      <c r="M36" t="n">
+        <v>-22.860802</v>
+      </c>
+      <c r="N36" t="n">
+        <v>-43.167526</v>
+      </c>
+      <c r="Q36" s="7" t="n">
+        <v>46297.45486111111</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="n">
+        <v>46298.43402777778</v>
+      </c>
+      <c r="M37" t="n">
+        <v>-23.346352</v>
+      </c>
+      <c r="N37" t="n">
+        <v>-43.0602</v>
+      </c>
+      <c r="Q37" s="7" t="n">
+        <v>46298.03541666667</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-10-05 11:51</t>
+        </is>
+      </c>
+      <c r="M38" t="n">
+        <v>-25.297014</v>
+      </c>
+      <c r="N38" t="n">
+        <v>-42.687855</v>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>2026-10-04 17:00</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:23</t>
+        </is>
+      </c>
+      <c r="M39" t="n">
+        <v>-22.892019</v>
+      </c>
+      <c r="N39" t="n">
+        <v>-43.191772</v>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:19</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-10-08 08:36</t>
+        </is>
+      </c>
+      <c r="M40" t="n">
+        <v>-23.923296</v>
+      </c>
+      <c r="N40" t="n">
+        <v>-42.987534</v>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>2026-10-07 00:43</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-10-12 10:22</t>
+        </is>
+      </c>
+      <c r="M41" t="n">
+        <v>-24.395149</v>
+      </c>
+      <c r="N41" t="n">
+        <v>-42.970379</v>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>2026-10-12 07:57</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-10-13 05:59</t>
+        </is>
+      </c>
+      <c r="M42" t="n">
+        <v>-24.395149</v>
+      </c>
+      <c r="N42" t="n">
+        <v>-42.970379</v>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>2026-10-12 07:57</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-10-14 14:10</t>
+        </is>
+      </c>
+      <c r="M43" t="n">
+        <v>-25.657743</v>
+      </c>
+      <c r="N43" t="n">
+        <v>-42.860188</v>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:56</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-10-15 07:21</t>
+        </is>
+      </c>
+      <c r="M44" t="n">
+        <v>-25.657743</v>
+      </c>
+      <c r="N44" t="n">
+        <v>-42.860188</v>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>2026-10-13 13:56</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-10-15 10:08</t>
+        </is>
+      </c>
+      <c r="M45" t="n">
+        <v>-23.520952</v>
+      </c>
+      <c r="N45" t="n">
+        <v>-43.070782</v>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>2026-10-15 09:27</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-10-18 09:38</t>
+        </is>
+      </c>
+      <c r="M46" t="n">
+        <v>-23.381544</v>
+      </c>
+      <c r="N46" t="n">
+        <v>-43.095318</v>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>2026-10-17 18:45</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>Underway by Sail</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:41</t>
+        </is>
+      </c>
+      <c r="M47" t="n">
+        <v>-22.89464</v>
+      </c>
+      <c r="N47" t="n">
+        <v>-43.2122</v>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:29</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>Moored</t>
         </is>
       </c>
     </row>
@@ -1793,10 +2806,10 @@
   <dimension ref="A1:S23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="10.5546875" customWidth="1" min="1" max="1"/>
+    <col width="26.33203125" customWidth="1" min="1" max="1"/>
     <col width="6.109375" customWidth="1" min="5" max="5"/>
     <col width="5.33203125" customWidth="1" min="6" max="6"/>
-    <col width="10.44140625" bestFit="1" customWidth="1" min="17" max="17"/>
+    <col width="21.77734375" customWidth="1" min="17" max="17"/>
     <col width="30.6640625" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
@@ -2342,7 +3355,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="12" t="n">
+      <c r="A22" s="7" t="n">
         <v>46278.86458333334</v>
       </c>
       <c r="M22" t="n">
@@ -2351,7 +3364,7 @@
       <c r="N22" t="n">
         <v>-41.020199</v>
       </c>
-      <c r="Q22" s="12" t="n">
+      <c r="Q22" s="7" t="n">
         <v>46278.86180555556</v>
       </c>
       <c r="S22" t="inlineStr">
@@ -2361,7 +3374,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="n">
+      <c r="A23" s="7" t="n">
         <v>46279.73333333333</v>
       </c>
       <c r="M23" t="n">
@@ -2370,7 +3383,7 @@
       <c r="N23" t="n">
         <v>-41.020283</v>
       </c>
-      <c r="Q23" s="12" t="n">
+      <c r="Q23" s="7" t="n">
         <v>46279.72847222222</v>
       </c>
       <c r="S23" t="inlineStr">
@@ -3024,7 +4037,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="n">
+      <c r="A23" s="7" t="n">
         <v>46278.86458333334</v>
       </c>
       <c r="M23" t="n">
@@ -3033,7 +4046,7 @@
       <c r="N23" t="n">
         <v>-42.644466</v>
       </c>
-      <c r="Q23" s="12" t="n">
+      <c r="Q23" s="7" t="n">
         <v>46278.78333333333</v>
       </c>
       <c r="S23" t="inlineStr">
@@ -3043,7 +4056,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="12" t="n">
+      <c r="A24" s="7" t="n">
         <v>46279.73333333333</v>
       </c>
       <c r="M24" t="n">
@@ -3052,7 +4065,7 @@
       <c r="N24" t="n">
         <v>-42.358501</v>
       </c>
-      <c r="Q24" s="12" t="n">
+      <c r="Q24" s="7" t="n">
         <v>46278.92222222222</v>
       </c>
       <c r="S24" t="inlineStr">
@@ -3626,7 +4639,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="12" t="n">
+      <c r="A22" s="7" t="n">
         <v>46278.86458333334</v>
       </c>
       <c r="M22" t="n">
@@ -3635,7 +4648,7 @@
       <c r="N22" t="n">
         <v>-42.652859</v>
       </c>
-      <c r="Q22" s="12" t="n">
+      <c r="Q22" s="7" t="n">
         <v>46277.40694444445</v>
       </c>
       <c r="S22" t="inlineStr">
@@ -3645,7 +4658,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="n">
+      <c r="A23" s="7" t="n">
         <v>46279.73333333333</v>
       </c>
       <c r="M23" t="n">
@@ -3654,7 +4667,7 @@
       <c r="N23" t="n">
         <v>-42.652859</v>
       </c>
-      <c r="Q23" s="12" t="n">
+      <c r="Q23" s="7" t="n">
         <v>46277.40694444445</v>
       </c>
       <c r="S23" t="inlineStr">
@@ -4310,7 +5323,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="n">
+      <c r="A23" s="7" t="n">
         <v>46278.86458333334</v>
       </c>
       <c r="M23" t="n">
@@ -4319,7 +5332,7 @@
       <c r="N23" t="n">
         <v>-42.51263</v>
       </c>
-      <c r="Q23" s="12" t="n">
+      <c r="Q23" s="7" t="n">
         <v>46278.53611111111</v>
       </c>
       <c r="S23" t="inlineStr">
@@ -4329,7 +5342,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="12" t="n">
+      <c r="A24" s="7" t="n">
         <v>46279.73333333333</v>
       </c>
       <c r="M24" t="n">
@@ -4338,7 +5351,7 @@
       <c r="N24" t="n">
         <v>-42.51263</v>
       </c>
-      <c r="Q24" s="12" t="n">
+      <c r="Q24" s="7" t="n">
         <v>46278.53611111111</v>
       </c>
       <c r="S24" t="inlineStr">
@@ -4359,7 +5372,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S23"/>
+  <dimension ref="A1:S53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="27.6640625" customWidth="1" style="8" min="1" max="1"/>
@@ -4968,7 +5981,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="12" t="n">
+      <c r="A22" s="7" t="n">
         <v>46278.85416666666</v>
       </c>
       <c r="M22" t="n">
@@ -4977,7 +5990,7 @@
       <c r="N22" t="n">
         <v>-39.828007</v>
       </c>
-      <c r="Q22" s="12" t="n">
+      <c r="Q22" s="7" t="n">
         <v>46277.68055555555</v>
       </c>
       <c r="S22" t="inlineStr">
@@ -4987,7 +6000,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="n">
+      <c r="A23" s="7" t="n">
         <v>46279.73333333333</v>
       </c>
       <c r="M23" t="n">
@@ -4996,18 +6009,645 @@
       <c r="N23" t="n">
         <v>-41.005341</v>
       </c>
-      <c r="Q23" s="12" t="n">
+      <c r="Q23" s="7" t="n">
         <v>46279.73333333333</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
           <t>Stopped</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="n">
+        <v>46280.53125</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-21.866369</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-41.015362</v>
+      </c>
+      <c r="Q24" s="7" t="n">
+        <v>46280.52847222222</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="n">
+        <v>46281.53472222222</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-21.881756</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-41.005352</v>
+      </c>
+      <c r="Q25" s="7" t="n">
+        <v>46281.52986111111</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="n">
+        <v>46281.62083333333</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-21.881727</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-41.005474</v>
+      </c>
+      <c r="Q26" s="7" t="n">
+        <v>46281.61666666667</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="n">
+        <v>46283.75694444445</v>
+      </c>
+      <c r="M27" t="n">
+        <v>-22.658087</v>
+      </c>
+      <c r="N27" t="n">
+        <v>-40.098728</v>
+      </c>
+      <c r="Q27" s="7" t="n">
+        <v>46283.66458333333</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="n">
+        <v>46287.35763888889</v>
+      </c>
+      <c r="M28" t="n">
+        <v>-21.881384</v>
+      </c>
+      <c r="N28" t="n">
+        <v>-41.005569</v>
+      </c>
+      <c r="Q28" s="7" t="n">
+        <v>46287.35625</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="n">
+        <v>46287.71666666667</v>
+      </c>
+      <c r="M29" t="n">
+        <v>-21.881159</v>
+      </c>
+      <c r="N29" t="n">
+        <v>-41.005726</v>
+      </c>
+      <c r="Q29" s="7" t="n">
+        <v>46287.7125</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="n">
+        <v>46288.26597222222</v>
+      </c>
+      <c r="M30" t="n">
+        <v>-22.53898</v>
+      </c>
+      <c r="N30" t="n">
+        <v>-40.563332</v>
+      </c>
+      <c r="Q30" s="7" t="n">
+        <v>46290.26180555556</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="n">
+        <v>46290.46666666667</v>
+      </c>
+      <c r="M31" t="n">
+        <v>-22.53898</v>
+      </c>
+      <c r="N31" t="n">
+        <v>-40.563332</v>
+      </c>
+      <c r="Q31" s="7" t="n">
+        <v>46290.26180555556</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="n">
+        <v>46291.32291666666</v>
+      </c>
+      <c r="M32" t="n">
+        <v>-22.53898</v>
+      </c>
+      <c r="N32" t="n">
+        <v>-40.563332</v>
+      </c>
+      <c r="Q32" s="7" t="n">
+        <v>46290.26180555556</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="n">
+        <v>46295.34652777778</v>
+      </c>
+      <c r="M33" t="n">
+        <v>-22.387238</v>
+      </c>
+      <c r="N33" t="n">
+        <v>-40.614143</v>
+      </c>
+      <c r="Q33" s="7" t="n">
+        <v>46295.06666666667</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="n">
+        <v>46296.35902777778</v>
+      </c>
+      <c r="M34" t="n">
+        <v>-21.893572</v>
+      </c>
+      <c r="N34" t="n">
+        <v>-40.932308</v>
+      </c>
+      <c r="Q34" s="7" t="n">
+        <v>46296.35625</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="n">
+        <v>46296.53263888889</v>
+      </c>
+      <c r="M35" t="n">
+        <v>-21.885771</v>
+      </c>
+      <c r="N35" t="n">
+        <v>-40.939201</v>
+      </c>
+      <c r="Q35" s="7" t="n">
+        <v>46296.53055555555</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="n">
+        <v>46296.65833333333</v>
+      </c>
+      <c r="M36" t="n">
+        <v>-21.886499</v>
+      </c>
+      <c r="N36" t="n">
+        <v>-40.939632</v>
+      </c>
+      <c r="Q36" s="7" t="n">
+        <v>46296.65</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="n">
+        <v>46297.45625</v>
+      </c>
+      <c r="M37" t="n">
+        <v>-21.920807</v>
+      </c>
+      <c r="N37" t="n">
+        <v>-40.867577</v>
+      </c>
+      <c r="Q37" s="7" t="n">
+        <v>46297.45486111111</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>Underway</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="n">
+        <v>46298.43402777778</v>
+      </c>
+      <c r="M38" t="n">
+        <v>-22.200331</v>
+      </c>
+      <c r="N38" t="n">
+        <v>-40.419418</v>
+      </c>
+      <c r="Q38" s="7" t="n">
+        <v>46298.37986111111</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="n">
+        <v>46298.88194444445</v>
+      </c>
+      <c r="M39" t="n">
+        <v>-21.888269</v>
+      </c>
+      <c r="N39" t="n">
+        <v>-40.936775</v>
+      </c>
+      <c r="Q39" s="7" t="n">
+        <v>46298.87777777778</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-10-05 11:51</t>
+        </is>
+      </c>
+      <c r="M40" t="n">
+        <v>-21.851984</v>
+      </c>
+      <c r="N40" t="n">
+        <v>-40.951046</v>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>2026-10-05 11:41</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:23</t>
+        </is>
+      </c>
+      <c r="M41" t="n">
+        <v>-21.859755</v>
+      </c>
+      <c r="N41" t="n">
+        <v>-41.019966</v>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:18</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-10-08 08:36</t>
+        </is>
+      </c>
+      <c r="M42" t="n">
+        <v>-21.859747</v>
+      </c>
+      <c r="N42" t="n">
+        <v>-41.020008</v>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>2026-10-08 08:33</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-10-12 10:22</t>
+        </is>
+      </c>
+      <c r="M43" t="n">
+        <v>-21.859756</v>
+      </c>
+      <c r="N43" t="n">
+        <v>-41.020008</v>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>2026-10-12 10:18</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-10-12 14:32</t>
+        </is>
+      </c>
+      <c r="M44" t="n">
+        <v>-21.859745</v>
+      </c>
+      <c r="N44" t="n">
+        <v>-41.02</v>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>2026-10-12 14:27</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-10-13 05:59</t>
+        </is>
+      </c>
+      <c r="M45" t="n">
+        <v>-21.859722</v>
+      </c>
+      <c r="N45" t="n">
+        <v>-41.020008</v>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>2026-10-13 05:57</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-10-13 09:26</t>
+        </is>
+      </c>
+      <c r="M46" t="n">
+        <v>-21.859699</v>
+      </c>
+      <c r="N46" t="n">
+        <v>-41.020008</v>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>2026-10-13 09:18</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-10-14 14:10</t>
+        </is>
+      </c>
+      <c r="M47" t="n">
+        <v>-21.859764</v>
+      </c>
+      <c r="N47" t="n">
+        <v>-41.019939</v>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>2026-10-14 14:06</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-10-14 15:06</t>
+        </is>
+      </c>
+      <c r="M48" t="n">
+        <v>-21.859781</v>
+      </c>
+      <c r="N48" t="n">
+        <v>-41.019932</v>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>2026-10-14 15:00</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-10-15 07:21</t>
+        </is>
+      </c>
+      <c r="M49" t="n">
+        <v>-21.859726</v>
+      </c>
+      <c r="N49" t="n">
+        <v>-41.019993</v>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>2026-10-15 07:15</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-10-15 10:08</t>
+        </is>
+      </c>
+      <c r="M50" t="n">
+        <v>-21.859743</v>
+      </c>
+      <c r="N50" t="n">
+        <v>-41.019981</v>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>2026-10-15 10:06</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-10-18 09:38</t>
+        </is>
+      </c>
+      <c r="M51" t="n">
+        <v>-21.860113</v>
+      </c>
+      <c r="N51" t="n">
+        <v>-41.019703</v>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>2026-10-18 09:31</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-10-18 14:49</t>
+        </is>
+      </c>
+      <c r="M52" t="n">
+        <v>-21.860121</v>
+      </c>
+      <c r="N52" t="n">
+        <v>-41.019688</v>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>2026-10-18 10:20</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:41</t>
+        </is>
+      </c>
+      <c r="M53" t="n">
+        <v>-21.860121</v>
+      </c>
+      <c r="N53" t="n">
+        <v>-41.019688</v>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>2026-10-18 10:20</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>Moored</t>
         </is>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:S15"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
@@ -5017,7 +6657,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S24"/>
+  <dimension ref="A1:S50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="34.44140625" customWidth="1" style="8" min="1" max="1"/>
@@ -5652,7 +7292,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="n">
+      <c r="A23" s="7" t="n">
         <v>46278.85416666666</v>
       </c>
       <c r="M23" t="n">
@@ -5661,7 +7301,7 @@
       <c r="N23" t="n">
         <v>-43.143887</v>
       </c>
-      <c r="Q23" s="12" t="n">
+      <c r="Q23" s="7" t="n">
         <v>46278.85069444445</v>
       </c>
       <c r="S23" t="inlineStr">
@@ -5671,7 +7311,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="12" t="n">
+      <c r="A24" s="7" t="n">
         <v>46279.73333333333</v>
       </c>
       <c r="M24" t="n">
@@ -5680,12 +7320,550 @@
       <c r="N24" t="n">
         <v>-43.143723</v>
       </c>
-      <c r="Q24" s="12" t="n">
+      <c r="Q24" s="7" t="n">
         <v>46279.73333333333</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
           <t>Stopped</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="n">
+        <v>46280.53125</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-22.843218</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-43.14378</v>
+      </c>
+      <c r="Q25" s="7" t="n">
+        <v>46280.52916666667</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="n">
+        <v>46281.53472222222</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-22.848108</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-43.148716</v>
+      </c>
+      <c r="Q26" s="7" t="n">
+        <v>46281.53055555555</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="n">
+        <v>46281.62083333333</v>
+      </c>
+      <c r="M27" t="n">
+        <v>-22.847336</v>
+      </c>
+      <c r="N27" t="n">
+        <v>-43.148479</v>
+      </c>
+      <c r="Q27" s="7" t="n">
+        <v>46281.61666666667</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="n">
+        <v>46283.75694444445</v>
+      </c>
+      <c r="M28" t="n">
+        <v>-22.847626</v>
+      </c>
+      <c r="N28" t="n">
+        <v>-43.149967</v>
+      </c>
+      <c r="Q28" s="7" t="n">
+        <v>46283.75416666667</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="n">
+        <v>46287.35763888889</v>
+      </c>
+      <c r="M29" t="n">
+        <v>-22.895662</v>
+      </c>
+      <c r="N29" t="n">
+        <v>-43.204994</v>
+      </c>
+      <c r="Q29" s="7" t="n">
+        <v>46287.35555555556</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="n">
+        <v>46287.71666666667</v>
+      </c>
+      <c r="M30" t="n">
+        <v>-22.895737</v>
+      </c>
+      <c r="N30" t="n">
+        <v>-43.205101</v>
+      </c>
+      <c r="Q30" s="7" t="n">
+        <v>46287.71180555555</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="n">
+        <v>46288.26597222222</v>
+      </c>
+      <c r="M31" t="n">
+        <v>-23.802383</v>
+      </c>
+      <c r="N31" t="n">
+        <v>-43.069859</v>
+      </c>
+      <c r="Q31" s="7" t="n">
+        <v>46288.66597222222</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="n">
+        <v>46290.46666666667</v>
+      </c>
+      <c r="M32" t="n">
+        <v>-23.802383</v>
+      </c>
+      <c r="N32" t="n">
+        <v>-43.069859</v>
+      </c>
+      <c r="Q32" s="7" t="n">
+        <v>46288.66597222222</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="n">
+        <v>46291.32291666666</v>
+      </c>
+      <c r="M33" t="n">
+        <v>-23.802383</v>
+      </c>
+      <c r="N33" t="n">
+        <v>-43.069859</v>
+      </c>
+      <c r="Q33" s="7" t="n">
+        <v>46288.66597222222</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="n">
+        <v>46295.34652777778</v>
+      </c>
+      <c r="M34" t="n">
+        <v>-25.002453</v>
+      </c>
+      <c r="N34" t="n">
+        <v>-42.564732</v>
+      </c>
+      <c r="Q34" s="7" t="n">
+        <v>46294.78055555555</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="n">
+        <v>46296.35902777778</v>
+      </c>
+      <c r="M35" t="n">
+        <v>-25.002453</v>
+      </c>
+      <c r="N35" t="n">
+        <v>-42.564732</v>
+      </c>
+      <c r="Q35" s="7" t="n">
+        <v>46294.78055555555</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="n">
+        <v>46296.53263888889</v>
+      </c>
+      <c r="M36" t="n">
+        <v>-25.002453</v>
+      </c>
+      <c r="N36" t="n">
+        <v>-42.564732</v>
+      </c>
+      <c r="Q36" s="7" t="n">
+        <v>46294.78055555555</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="n">
+        <v>46297.45625</v>
+      </c>
+      <c r="M37" t="n">
+        <v>-22.847294</v>
+      </c>
+      <c r="N37" t="n">
+        <v>-43.150326</v>
+      </c>
+      <c r="Q37" s="7" t="n">
+        <v>46297.45277777778</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="n">
+        <v>46298.43402777778</v>
+      </c>
+      <c r="M38" t="n">
+        <v>-22.888092</v>
+      </c>
+      <c r="N38" t="n">
+        <v>-43.215275</v>
+      </c>
+      <c r="Q38" s="7" t="n">
+        <v>46298.43263888889</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="n">
+        <v>46298.88194444445</v>
+      </c>
+      <c r="M39" t="n">
+        <v>-22.8881</v>
+      </c>
+      <c r="N39" t="n">
+        <v>-43.21526</v>
+      </c>
+      <c r="Q39" s="7" t="n">
+        <v>46298.87847222222</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-10-05 11:51</t>
+        </is>
+      </c>
+      <c r="M40" t="n">
+        <v>-22.384573</v>
+      </c>
+      <c r="N40" t="n">
+        <v>-41.768406</v>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>2026-10-05 11:46</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:23</t>
+        </is>
+      </c>
+      <c r="M41" t="n">
+        <v>-23.056662</v>
+      </c>
+      <c r="N41" t="n">
+        <v>-41.825161</v>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>2026-10-05 20:27</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-10-08 08:36</t>
+        </is>
+      </c>
+      <c r="M42" t="n">
+        <v>-23.056662</v>
+      </c>
+      <c r="N42" t="n">
+        <v>-41.825161</v>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>2026-10-05 20:27</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-10-12 10:22</t>
+        </is>
+      </c>
+      <c r="M43" t="n">
+        <v>-22.895639</v>
+      </c>
+      <c r="N43" t="n">
+        <v>-43.204945</v>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>2026-10-12 10:18</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-10-12 14:32</t>
+        </is>
+      </c>
+      <c r="M44" t="n">
+        <v>-22.89567</v>
+      </c>
+      <c r="N44" t="n">
+        <v>-43.204952</v>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>2026-10-12 14:24</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-10-13 05:59</t>
+        </is>
+      </c>
+      <c r="M45" t="n">
+        <v>-23.234547</v>
+      </c>
+      <c r="N45" t="n">
+        <v>-43.01862</v>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>2026-10-12 21:00</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>Underway by Sail</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-10-14 14:10</t>
+        </is>
+      </c>
+      <c r="M46" t="n">
+        <v>-23.234547</v>
+      </c>
+      <c r="N46" t="n">
+        <v>-43.01862</v>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>2026-10-12 21:00</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>Underway by Sail</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-10-15 07:21</t>
+        </is>
+      </c>
+      <c r="M47" t="n">
+        <v>-23.234547</v>
+      </c>
+      <c r="N47" t="n">
+        <v>-43.01862</v>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>2026-10-12 21:00</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>Underway by Sail</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-10-18 09:38</t>
+        </is>
+      </c>
+      <c r="M48" t="n">
+        <v>-23.657549</v>
+      </c>
+      <c r="N48" t="n">
+        <v>-42.807114</v>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>2026-10-18 08:54</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-10-18 14:49</t>
+        </is>
+      </c>
+      <c r="M49" t="n">
+        <v>-23.919956</v>
+      </c>
+      <c r="N49" t="n">
+        <v>-42.676239</v>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>2026-10-18 11:29</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:41</t>
+        </is>
+      </c>
+      <c r="M50" t="n">
+        <v>-25.007244</v>
+      </c>
+      <c r="N50" t="n">
+        <v>-42.400146</v>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>2026-10-21 17:27</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
         </is>
       </c>
     </row>
@@ -5701,7 +7879,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S26"/>
+  <dimension ref="A1:S56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="25.33203125" customWidth="1" style="8" min="1" max="1"/>
@@ -6404,7 +8582,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="12" t="n">
+      <c r="A25" s="7" t="n">
         <v>46278.85416666666</v>
       </c>
       <c r="M25" t="n">
@@ -6413,7 +8591,7 @@
       <c r="N25" t="n">
         <v>-43.122807</v>
       </c>
-      <c r="Q25" s="12" t="n">
+      <c r="Q25" s="7" t="n">
         <v>46278.85138888889</v>
       </c>
       <c r="S25" t="inlineStr">
@@ -6423,7 +8601,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="12" t="n">
+      <c r="A26" s="7" t="n">
         <v>46279.73333333333</v>
       </c>
       <c r="M26" t="n">
@@ -6432,12 +8610,638 @@
       <c r="N26" t="n">
         <v>-43.122875</v>
       </c>
-      <c r="Q26" s="12" t="n">
+      <c r="Q26" s="7" t="n">
         <v>46279.73263888889</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
           <t>Moored</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="n">
+        <v>46280.53125</v>
+      </c>
+      <c r="M27" t="n">
+        <v>-22.870699</v>
+      </c>
+      <c r="N27" t="n">
+        <v>-43.122826</v>
+      </c>
+      <c r="Q27" s="7" t="n">
+        <v>46280.52847222222</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="n">
+        <v>46281.53472222222</v>
+      </c>
+      <c r="M28" t="n">
+        <v>-22.870749</v>
+      </c>
+      <c r="N28" t="n">
+        <v>-43.12286</v>
+      </c>
+      <c r="Q28" s="7" t="n">
+        <v>46281.53055555555</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="n">
+        <v>46281.62083333333</v>
+      </c>
+      <c r="M29" t="n">
+        <v>-22.870773</v>
+      </c>
+      <c r="N29" t="n">
+        <v>-43.122822</v>
+      </c>
+      <c r="Q29" s="7" t="n">
+        <v>46281.61805555555</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="n">
+        <v>46283.75694444445</v>
+      </c>
+      <c r="M30" t="n">
+        <v>-22.870728</v>
+      </c>
+      <c r="N30" t="n">
+        <v>-43.122807</v>
+      </c>
+      <c r="Q30" s="7" t="n">
+        <v>46283.75347222222</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="n">
+        <v>46287.35763888889</v>
+      </c>
+      <c r="M31" t="n">
+        <v>-22.843082</v>
+      </c>
+      <c r="N31" t="n">
+        <v>-43.148041</v>
+      </c>
+      <c r="Q31" s="7" t="n">
+        <v>46287.35625</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="n">
+        <v>46287.71666666667</v>
+      </c>
+      <c r="M32" t="n">
+        <v>-22.843645</v>
+      </c>
+      <c r="N32" t="n">
+        <v>-43.148087</v>
+      </c>
+      <c r="Q32" s="7" t="n">
+        <v>46287.71458333333</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="n">
+        <v>46288.26597222222</v>
+      </c>
+      <c r="M33" t="n">
+        <v>-22.848188</v>
+      </c>
+      <c r="N33" t="n">
+        <v>-43.14082</v>
+      </c>
+      <c r="Q33" s="7" t="n">
+        <v>46290.38125</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="n">
+        <v>46290.46666666667</v>
+      </c>
+      <c r="M34" t="n">
+        <v>-22.84737</v>
+      </c>
+      <c r="N34" t="n">
+        <v>-43.140388</v>
+      </c>
+      <c r="Q34" s="7" t="n">
+        <v>46290.4625</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="n">
+        <v>46291.32291666666</v>
+      </c>
+      <c r="M35" t="n">
+        <v>-22.848148</v>
+      </c>
+      <c r="N35" t="n">
+        <v>-43.140644</v>
+      </c>
+      <c r="Q35" s="7" t="n">
+        <v>46291.31875</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="n">
+        <v>46295.34652777778</v>
+      </c>
+      <c r="M36" t="n">
+        <v>-22.36775</v>
+      </c>
+      <c r="N36" t="n">
+        <v>-41.750183</v>
+      </c>
+      <c r="Q36" s="7" t="n">
+        <v>46295.34583333333</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="n">
+        <v>46296.35902777778</v>
+      </c>
+      <c r="M37" t="n">
+        <v>-21.863632</v>
+      </c>
+      <c r="N37" t="n">
+        <v>-41.017132</v>
+      </c>
+      <c r="Q37" s="7" t="n">
+        <v>46296.35625</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="n">
+        <v>46296.53263888889</v>
+      </c>
+      <c r="M38" t="n">
+        <v>-21.939144</v>
+      </c>
+      <c r="N38" t="n">
+        <v>-40.803909</v>
+      </c>
+      <c r="Q38" s="7" t="n">
+        <v>46296.50902777778</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="n">
+        <v>46296.65833333333</v>
+      </c>
+      <c r="M39" t="n">
+        <v>-22.307146</v>
+      </c>
+      <c r="N39" t="n">
+        <v>-40.435665</v>
+      </c>
+      <c r="Q39" s="7" t="n">
+        <v>46296.63472222222</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="n">
+        <v>46297.45625</v>
+      </c>
+      <c r="M40" t="n">
+        <v>-22.358698</v>
+      </c>
+      <c r="N40" t="n">
+        <v>-40.36393</v>
+      </c>
+      <c r="Q40" s="7" t="n">
+        <v>46296.65555555555</v>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="n">
+        <v>46298.43402777778</v>
+      </c>
+      <c r="M41" t="n">
+        <v>-22.563892</v>
+      </c>
+      <c r="N41" t="n">
+        <v>-40.310486</v>
+      </c>
+      <c r="Q41" s="7" t="n">
+        <v>46298.39375</v>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="n">
+        <v>46298.88194444445</v>
+      </c>
+      <c r="M42" t="n">
+        <v>-22.562277</v>
+      </c>
+      <c r="N42" t="n">
+        <v>-40.538582</v>
+      </c>
+      <c r="Q42" s="7" t="n">
+        <v>46298.78541666667</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-10-05 11:51</t>
+        </is>
+      </c>
+      <c r="M43" t="n">
+        <v>-21.863888</v>
+      </c>
+      <c r="N43" t="n">
+        <v>-41.016933</v>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>2026-10-05 11:49</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:23</t>
+        </is>
+      </c>
+      <c r="M44" t="n">
+        <v>-21.881781</v>
+      </c>
+      <c r="N44" t="n">
+        <v>-41.006062</v>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:04</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-10-08 08:36</t>
+        </is>
+      </c>
+      <c r="M45" t="n">
+        <v>-22.474859</v>
+      </c>
+      <c r="N45" t="n">
+        <v>-40.951912</v>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>2026-10-07 23:35</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>Underway</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-10-12 10:22</t>
+        </is>
+      </c>
+      <c r="M46" t="n">
+        <v>-21.848089</v>
+      </c>
+      <c r="N46" t="n">
+        <v>-40.958847</v>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>2026-10-12 10:18</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-10-12 14:32</t>
+        </is>
+      </c>
+      <c r="M47" t="n">
+        <v>-21.847813</v>
+      </c>
+      <c r="N47" t="n">
+        <v>-40.959354</v>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>2026-10-12 14:24</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-10-13 05:59</t>
+        </is>
+      </c>
+      <c r="M48" t="n">
+        <v>-21.847652</v>
+      </c>
+      <c r="N48" t="n">
+        <v>-40.959175</v>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>2026-10-13 05:54</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-10-13 09:26</t>
+        </is>
+      </c>
+      <c r="M49" t="n">
+        <v>-21.84787</v>
+      </c>
+      <c r="N49" t="n">
+        <v>-40.959198</v>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>2026-10-13 09:15</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-10-14 14:10</t>
+        </is>
+      </c>
+      <c r="M50" t="n">
+        <v>-21.848049</v>
+      </c>
+      <c r="N50" t="n">
+        <v>-40.959053</v>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>2026-10-14 14:06</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-10-14 15:06</t>
+        </is>
+      </c>
+      <c r="M51" t="n">
+        <v>-21.847815</v>
+      </c>
+      <c r="N51" t="n">
+        <v>-40.959183</v>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>2026-10-14 15:00</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-10-15 07:21</t>
+        </is>
+      </c>
+      <c r="M52" t="n">
+        <v>-21.847891</v>
+      </c>
+      <c r="N52" t="n">
+        <v>-40.958805</v>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>2026-10-15 07:15</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-10-15 10:08</t>
+        </is>
+      </c>
+      <c r="M53" t="n">
+        <v>-21.847805</v>
+      </c>
+      <c r="N53" t="n">
+        <v>-40.959217</v>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>2026-10-15 10:00</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-10-18 09:38</t>
+        </is>
+      </c>
+      <c r="M54" t="n">
+        <v>-21.983027</v>
+      </c>
+      <c r="N54" t="n">
+        <v>-40.765236</v>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>2026-10-18 08:10</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>Underway by Sail</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-10-18 14:49</t>
+        </is>
+      </c>
+      <c r="M55" t="n">
+        <v>-22.370632</v>
+      </c>
+      <c r="N55" t="n">
+        <v>-41.723354</v>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>2026-10-18 14:46</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>Underway by Sail</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:41</t>
+        </is>
+      </c>
+      <c r="M56" t="n">
+        <v>-22.385712</v>
+      </c>
+      <c r="N56" t="n">
+        <v>-41.616428</v>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>2026-10-23 00:00</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>Underway by Sail</t>
         </is>
       </c>
     </row>
@@ -6453,7 +9257,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S24"/>
+  <dimension ref="A1:S47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="23.33203125" customWidth="1" style="8" min="1" max="1"/>
@@ -7087,7 +9891,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="n">
+      <c r="A23" s="7" t="n">
         <v>46278.85416666666</v>
       </c>
       <c r="M23" t="n">
@@ -7096,7 +9900,7 @@
       <c r="N23" t="n">
         <v>-42.883278</v>
       </c>
-      <c r="Q23" s="12" t="n">
+      <c r="Q23" s="7" t="n">
         <v>46276.55486111111</v>
       </c>
       <c r="S23" t="inlineStr">
@@ -7106,7 +9910,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="12" t="n">
+      <c r="A24" s="7" t="n">
         <v>46279.73333333333</v>
       </c>
       <c r="M24" t="n">
@@ -7115,12 +9919,489 @@
       <c r="N24" t="n">
         <v>-42.883278</v>
       </c>
-      <c r="Q24" s="12" t="n">
+      <c r="Q24" s="7" t="n">
         <v>46276.55486111111</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
           <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="n">
+        <v>46280.53125</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-23.822506</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-42.883278</v>
+      </c>
+      <c r="Q25" s="7" t="n">
+        <v>46276.55486111111</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="n">
+        <v>46281.53472222222</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-23.822506</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-42.883278</v>
+      </c>
+      <c r="Q26" s="7" t="n">
+        <v>46276.55486111111</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="n">
+        <v>46283.75694444445</v>
+      </c>
+      <c r="M27" t="n">
+        <v>-23.822506</v>
+      </c>
+      <c r="N27" t="n">
+        <v>-42.883278</v>
+      </c>
+      <c r="Q27" s="7" t="n">
+        <v>46276.55486111111</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="n">
+        <v>46287.35763888889</v>
+      </c>
+      <c r="M28" t="n">
+        <v>-22.893711</v>
+      </c>
+      <c r="N28" t="n">
+        <v>-43.212608</v>
+      </c>
+      <c r="Q28" s="7" t="n">
+        <v>46287.35486111111</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="n">
+        <v>46287.71666666667</v>
+      </c>
+      <c r="M29" t="n">
+        <v>-22.851999</v>
+      </c>
+      <c r="N29" t="n">
+        <v>-43.141842</v>
+      </c>
+      <c r="Q29" s="7" t="n">
+        <v>46287.71319444444</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="n">
+        <v>46288.26597222222</v>
+      </c>
+      <c r="M30" t="n">
+        <v>-25.796001</v>
+      </c>
+      <c r="N30" t="n">
+        <v>-43.236515</v>
+      </c>
+      <c r="Q30" s="7" t="n">
+        <v>46289.41458333333</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="n">
+        <v>46290.46666666667</v>
+      </c>
+      <c r="M31" t="n">
+        <v>-25.796001</v>
+      </c>
+      <c r="N31" t="n">
+        <v>-43.236515</v>
+      </c>
+      <c r="Q31" s="7" t="n">
+        <v>46289.41458333333</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="n">
+        <v>46291.32291666666</v>
+      </c>
+      <c r="M32" t="n">
+        <v>-25.796001</v>
+      </c>
+      <c r="N32" t="n">
+        <v>-43.236515</v>
+      </c>
+      <c r="Q32" s="7" t="n">
+        <v>46289.41458333333</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="n">
+        <v>46295.34652777778</v>
+      </c>
+      <c r="M33" t="n">
+        <v>-22.8937</v>
+      </c>
+      <c r="N33" t="n">
+        <v>-43.212608</v>
+      </c>
+      <c r="Q33" s="7" t="n">
+        <v>46295.34583333333</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="n">
+        <v>46296.35902777778</v>
+      </c>
+      <c r="M34" t="n">
+        <v>-23.480049</v>
+      </c>
+      <c r="N34" t="n">
+        <v>-43.003395</v>
+      </c>
+      <c r="Q34" s="7" t="n">
+        <v>46295.77430555555</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="n">
+        <v>46296.53263888889</v>
+      </c>
+      <c r="M35" t="n">
+        <v>-23.480049</v>
+      </c>
+      <c r="N35" t="n">
+        <v>-43.003395</v>
+      </c>
+      <c r="Q35" s="7" t="n">
+        <v>46295.77430555555</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="n">
+        <v>46297.45625</v>
+      </c>
+      <c r="M36" t="n">
+        <v>-23.480049</v>
+      </c>
+      <c r="N36" t="n">
+        <v>-43.003395</v>
+      </c>
+      <c r="Q36" s="7" t="n">
+        <v>46295.77430555555</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="n">
+        <v>46298.43402777778</v>
+      </c>
+      <c r="M37" t="n">
+        <v>-23.480049</v>
+      </c>
+      <c r="N37" t="n">
+        <v>-43.003395</v>
+      </c>
+      <c r="Q37" s="7" t="n">
+        <v>46295.77430555555</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-10-05 11:51</t>
+        </is>
+      </c>
+      <c r="M38" t="n">
+        <v>-22.860834</v>
+      </c>
+      <c r="N38" t="n">
+        <v>-43.185333</v>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>2026-10-05 11:46</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:23</t>
+        </is>
+      </c>
+      <c r="M39" t="n">
+        <v>-22.892347</v>
+      </c>
+      <c r="N39" t="n">
+        <v>-43.213284</v>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:08</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-10-08 08:36</t>
+        </is>
+      </c>
+      <c r="M40" t="n">
+        <v>-23.93251</v>
+      </c>
+      <c r="N40" t="n">
+        <v>-42.867908</v>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>2026-10-08 02:01</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-10-12 10:22</t>
+        </is>
+      </c>
+      <c r="M41" t="n">
+        <v>-23.93251</v>
+      </c>
+      <c r="N41" t="n">
+        <v>-42.867908</v>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>2026-10-08 02:01</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-10-13 05:59</t>
+        </is>
+      </c>
+      <c r="M42" t="n">
+        <v>-23.93251</v>
+      </c>
+      <c r="N42" t="n">
+        <v>-42.867908</v>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>2026-10-08 02:01</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-10-14 14:10</t>
+        </is>
+      </c>
+      <c r="M43" t="n">
+        <v>-23.93251</v>
+      </c>
+      <c r="N43" t="n">
+        <v>-42.867908</v>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>2026-10-08 02:01</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-10-15 07:21</t>
+        </is>
+      </c>
+      <c r="M44" t="n">
+        <v>-23.93251</v>
+      </c>
+      <c r="N44" t="n">
+        <v>-42.867908</v>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>2026-10-08 02:01</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-10-18 09:38</t>
+        </is>
+      </c>
+      <c r="M45" t="n">
+        <v>-22.850307</v>
+      </c>
+      <c r="N45" t="n">
+        <v>-43.149681</v>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>2026-10-18 09:34</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-10-18 14:49</t>
+        </is>
+      </c>
+      <c r="M46" t="n">
+        <v>-22.8946</v>
+      </c>
+      <c r="N46" t="n">
+        <v>-43.212158</v>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>2026-10-18 14:46</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:41</t>
+        </is>
+      </c>
+      <c r="M47" t="n">
+        <v>-22.989149</v>
+      </c>
+      <c r="N47" t="n">
+        <v>-43.126095</v>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>2026-10-21 13:55</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>Underway</t>
         </is>
       </c>
     </row>
@@ -7136,7 +10417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S24"/>
+  <dimension ref="A1:S52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="23.6640625" customWidth="1" style="8" min="1" max="1"/>
@@ -7773,7 +11054,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="n">
+      <c r="A23" s="7" t="n">
         <v>46278.85416666666</v>
       </c>
       <c r="M23" t="n">
@@ -7782,7 +11063,7 @@
       <c r="N23" t="n">
         <v>-39.956585</v>
       </c>
-      <c r="Q23" s="12" t="n">
+      <c r="Q23" s="7" t="n">
         <v>46276.88958333333</v>
       </c>
       <c r="S23" t="inlineStr">
@@ -7792,7 +11073,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="12" t="n">
+      <c r="A24" s="7" t="n">
         <v>46279.73333333333</v>
       </c>
       <c r="M24" t="n">
@@ -7801,12 +11082,592 @@
       <c r="N24" t="n">
         <v>-40.945045</v>
       </c>
-      <c r="Q24" s="12" t="n">
+      <c r="Q24" s="7" t="n">
         <v>46279.73263888889</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
           <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="n">
+        <v>46280.53125</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-21.862123</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-41.018005</v>
+      </c>
+      <c r="Q25" s="7" t="n">
+        <v>46280.52916666667</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="n">
+        <v>46281.53472222222</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-21.862129</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-41.017979</v>
+      </c>
+      <c r="Q26" s="7" t="n">
+        <v>46281.52916666667</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="n">
+        <v>46281.62083333333</v>
+      </c>
+      <c r="M27" t="n">
+        <v>-21.862131</v>
+      </c>
+      <c r="N27" t="n">
+        <v>-41.01796</v>
+      </c>
+      <c r="Q27" s="7" t="n">
+        <v>46281.61666666667</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="n">
+        <v>46283.75694444445</v>
+      </c>
+      <c r="M28" t="n">
+        <v>-22.495092</v>
+      </c>
+      <c r="N28" t="n">
+        <v>-40.335285</v>
+      </c>
+      <c r="Q28" s="7" t="n">
+        <v>46283.61180555556</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>Restricted Manoeuvrability</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="n">
+        <v>46287.35763888889</v>
+      </c>
+      <c r="M29" t="n">
+        <v>-22.647787</v>
+      </c>
+      <c r="N29" t="n">
+        <v>-40.254414</v>
+      </c>
+      <c r="Q29" s="7" t="n">
+        <v>46287.16527777778</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>Restricted Manoeuvrability</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="n">
+        <v>46287.71666666667</v>
+      </c>
+      <c r="M30" t="n">
+        <v>-22.468473</v>
+      </c>
+      <c r="N30" t="n">
+        <v>-40.007927</v>
+      </c>
+      <c r="Q30" s="7" t="n">
+        <v>46287.67430555556</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>Restricted Manoeuvrability</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="n">
+        <v>46288.26597222222</v>
+      </c>
+      <c r="M31" t="n">
+        <v>-22.422646</v>
+      </c>
+      <c r="N31" t="n">
+        <v>-39.957474</v>
+      </c>
+      <c r="Q31" s="7" t="n">
+        <v>46290.28402777778</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>Restricted Manoeuvrability</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="n">
+        <v>46290.46666666667</v>
+      </c>
+      <c r="M32" t="n">
+        <v>-22.422646</v>
+      </c>
+      <c r="N32" t="n">
+        <v>-39.957474</v>
+      </c>
+      <c r="Q32" s="7" t="n">
+        <v>46290.28402777778</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>Restricted Manoeuvrability</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="n">
+        <v>46291.32291666666</v>
+      </c>
+      <c r="M33" t="n">
+        <v>-22.088587</v>
+      </c>
+      <c r="N33" t="n">
+        <v>-39.870125</v>
+      </c>
+      <c r="Q33" s="7" t="n">
+        <v>46291.29236111111</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>Restricted Manoeuvrability</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="n">
+        <v>46295.34652777778</v>
+      </c>
+      <c r="M34" t="n">
+        <v>-20.32081</v>
+      </c>
+      <c r="N34" t="n">
+        <v>-40.305046</v>
+      </c>
+      <c r="Q34" s="7" t="n">
+        <v>46295.34583333333</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="n">
+        <v>46296.35902777778</v>
+      </c>
+      <c r="M35" t="n">
+        <v>-22.43532</v>
+      </c>
+      <c r="N35" t="n">
+        <v>-39.952579</v>
+      </c>
+      <c r="Q35" s="7" t="n">
+        <v>46296.34097222222</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="n">
+        <v>46296.53263888889</v>
+      </c>
+      <c r="M36" t="n">
+        <v>-22.418043</v>
+      </c>
+      <c r="N36" t="n">
+        <v>-39.953278</v>
+      </c>
+      <c r="Q36" s="7" t="n">
+        <v>46296.51944444444</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="n">
+        <v>46296.65833333333</v>
+      </c>
+      <c r="M37" t="n">
+        <v>-22.419659</v>
+      </c>
+      <c r="N37" t="n">
+        <v>-39.955727</v>
+      </c>
+      <c r="Q37" s="7" t="n">
+        <v>46296.59305555555</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="n">
+        <v>46297.45625</v>
+      </c>
+      <c r="M38" t="n">
+        <v>-22.422876</v>
+      </c>
+      <c r="N38" t="n">
+        <v>-39.957352</v>
+      </c>
+      <c r="Q38" s="7" t="n">
+        <v>46297.45069444444</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="n">
+        <v>46298.43402777778</v>
+      </c>
+      <c r="M39" t="n">
+        <v>-22.422651</v>
+      </c>
+      <c r="N39" t="n">
+        <v>-39.957432</v>
+      </c>
+      <c r="Q39" s="7" t="n">
+        <v>46298.24236111111</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="n">
+        <v>46298.88194444445</v>
+      </c>
+      <c r="M40" t="n">
+        <v>-21.915573</v>
+      </c>
+      <c r="N40" t="n">
+        <v>-39.749012</v>
+      </c>
+      <c r="Q40" s="7" t="n">
+        <v>46298.85972222222</v>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-10-05 11:51</t>
+        </is>
+      </c>
+      <c r="M41" t="n">
+        <v>-21.941364</v>
+      </c>
+      <c r="N41" t="n">
+        <v>-39.765244</v>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>2026-10-05 11:43</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>Restricted Manoeuvrability</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:23</t>
+        </is>
+      </c>
+      <c r="M42" t="n">
+        <v>-21.941174</v>
+      </c>
+      <c r="N42" t="n">
+        <v>-39.765396</v>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:13</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>Restricted Manoeuvrability</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-10-08 08:36</t>
+        </is>
+      </c>
+      <c r="M43" t="n">
+        <v>-22.562679</v>
+      </c>
+      <c r="N43" t="n">
+        <v>-40.063881</v>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>2026-10-08 06:51</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>Restricted Manoeuvrability</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-10-12 10:22</t>
+        </is>
+      </c>
+      <c r="M44" t="n">
+        <v>-22.565886</v>
+      </c>
+      <c r="N44" t="n">
+        <v>-40.062073</v>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>2026-10-12 03:33</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>Restricted Manoeuvrability</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-10-12 14:32</t>
+        </is>
+      </c>
+      <c r="M45" t="n">
+        <v>-22.563986</v>
+      </c>
+      <c r="N45" t="n">
+        <v>-40.063755</v>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>2026-10-12 14:21</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>Restricted Manoeuvrability</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-10-13 05:59</t>
+        </is>
+      </c>
+      <c r="M46" t="n">
+        <v>-22.372114</v>
+      </c>
+      <c r="N46" t="n">
+        <v>-41.74469</v>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>2026-10-13 05:56</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-10-13 09:26</t>
+        </is>
+      </c>
+      <c r="M47" t="n">
+        <v>-22.383398</v>
+      </c>
+      <c r="N47" t="n">
+        <v>-41.76775</v>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>2026-10-13 09:16</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-10-14 14:10</t>
+        </is>
+      </c>
+      <c r="M48" t="n">
+        <v>-22.439482</v>
+      </c>
+      <c r="N48" t="n">
+        <v>-40.423332</v>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>2026-10-14 11:27</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-10-15 07:21</t>
+        </is>
+      </c>
+      <c r="M49" t="n">
+        <v>-22.125532</v>
+      </c>
+      <c r="N49" t="n">
+        <v>-39.973827</v>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>2026-10-15 07:12</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>Restricted Manoeuvrability</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-10-18 09:38</t>
+        </is>
+      </c>
+      <c r="M50" t="n">
+        <v>-21.906002</v>
+      </c>
+      <c r="N50" t="n">
+        <v>-39.736813</v>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>2026-10-18 07:37</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>Restricted Manoeuvrability</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-10-18 14:49</t>
+        </is>
+      </c>
+      <c r="M51" t="n">
+        <v>-21.901966</v>
+      </c>
+      <c r="N51" t="n">
+        <v>-39.738735</v>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>2026-10-18 10:07</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>Restricted Manoeuvrability</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:41</t>
+        </is>
+      </c>
+      <c r="M52" t="n">
+        <v>-21.908558</v>
+      </c>
+      <c r="N52" t="n">
+        <v>-39.755409</v>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>2026-10-23 10:53</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>Restricted Manoeuvrability</t>
         </is>
       </c>
     </row>
@@ -7822,7 +11683,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S24"/>
+  <dimension ref="A1:S51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="39.6640625" customWidth="1" style="8" min="1" max="1"/>
@@ -8456,7 +12317,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="n">
+      <c r="A23" s="7" t="n">
         <v>46278.85416666666</v>
       </c>
       <c r="M23" t="n">
@@ -8465,7 +12326,7 @@
       <c r="N23" t="n">
         <v>-43.182495</v>
       </c>
-      <c r="Q23" s="12" t="n">
+      <c r="Q23" s="7" t="n">
         <v>46278.85208333333</v>
       </c>
       <c r="S23" t="inlineStr">
@@ -8475,7 +12336,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="12" t="n">
+      <c r="A24" s="7" t="n">
         <v>46279.73333333333</v>
       </c>
       <c r="M24" t="n">
@@ -8484,12 +12345,573 @@
       <c r="N24" t="n">
         <v>-42.994446</v>
       </c>
-      <c r="Q24" s="12" t="n">
+      <c r="Q24" s="7" t="n">
         <v>46279.21597222222</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
           <t>Underway</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="n">
+        <v>46280.53125</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-23.310389</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-42.994446</v>
+      </c>
+      <c r="Q25" s="7" t="n">
+        <v>46279.21597222222</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>Underway</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="n">
+        <v>46281.53472222222</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-23.310389</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-42.994446</v>
+      </c>
+      <c r="Q26" s="7" t="n">
+        <v>46279.21597222222</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>Underway</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="n">
+        <v>46283.75694444445</v>
+      </c>
+      <c r="M27" t="n">
+        <v>-23.310389</v>
+      </c>
+      <c r="N27" t="n">
+        <v>-42.994446</v>
+      </c>
+      <c r="Q27" s="7" t="n">
+        <v>46279.21597222222</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>Underway</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="n">
+        <v>46287.35763888889</v>
+      </c>
+      <c r="M28" t="n">
+        <v>-22.847887</v>
+      </c>
+      <c r="N28" t="n">
+        <v>-43.149258</v>
+      </c>
+      <c r="Q28" s="7" t="n">
+        <v>46287.35625</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="n">
+        <v>46287.71666666667</v>
+      </c>
+      <c r="M29" t="n">
+        <v>-22.932316</v>
+      </c>
+      <c r="N29" t="n">
+        <v>-43.140091</v>
+      </c>
+      <c r="Q29" s="7" t="n">
+        <v>46287.71527777778</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="n">
+        <v>46288.26597222222</v>
+      </c>
+      <c r="M30" t="n">
+        <v>-24.546144</v>
+      </c>
+      <c r="N30" t="n">
+        <v>-42.448387</v>
+      </c>
+      <c r="Q30" s="7" t="n">
+        <v>46288.22083333333</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="n">
+        <v>46290.46666666667</v>
+      </c>
+      <c r="M31" t="n">
+        <v>-24.546144</v>
+      </c>
+      <c r="N31" t="n">
+        <v>-42.448387</v>
+      </c>
+      <c r="Q31" s="7" t="n">
+        <v>46288.22083333333</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="n">
+        <v>46291.32291666666</v>
+      </c>
+      <c r="M32" t="n">
+        <v>-23.15801</v>
+      </c>
+      <c r="N32" t="n">
+        <v>-43.062328</v>
+      </c>
+      <c r="Q32" s="7" t="n">
+        <v>46291.31180555555</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="n">
+        <v>46295.34652777778</v>
+      </c>
+      <c r="M33" t="n">
+        <v>-22.881624</v>
+      </c>
+      <c r="N33" t="n">
+        <v>-43.117432</v>
+      </c>
+      <c r="Q33" s="7" t="n">
+        <v>46295.34444444445</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="n">
+        <v>46296.35902777778</v>
+      </c>
+      <c r="M34" t="n">
+        <v>-22.847975</v>
+      </c>
+      <c r="N34" t="n">
+        <v>-43.149502</v>
+      </c>
+      <c r="Q34" s="7" t="n">
+        <v>46296.35625</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="n">
+        <v>46296.53263888889</v>
+      </c>
+      <c r="M35" t="n">
+        <v>-22.847759</v>
+      </c>
+      <c r="N35" t="n">
+        <v>-43.149666</v>
+      </c>
+      <c r="Q35" s="7" t="n">
+        <v>46296.52708333333</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="n">
+        <v>46296.65833333333</v>
+      </c>
+      <c r="M36" t="n">
+        <v>-22.846704</v>
+      </c>
+      <c r="N36" t="n">
+        <v>-43.148815</v>
+      </c>
+      <c r="Q36" s="7" t="n">
+        <v>46296.65416666667</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="n">
+        <v>46297.45625</v>
+      </c>
+      <c r="M37" t="n">
+        <v>-22.893728</v>
+      </c>
+      <c r="N37" t="n">
+        <v>-43.212635</v>
+      </c>
+      <c r="Q37" s="7" t="n">
+        <v>46297.45347222222</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="n">
+        <v>46298.43402777778</v>
+      </c>
+      <c r="M38" t="n">
+        <v>-23.403748</v>
+      </c>
+      <c r="N38" t="n">
+        <v>-42.94437</v>
+      </c>
+      <c r="Q38" s="7" t="n">
+        <v>46298.27222222222</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="n">
+        <v>46298.88194444445</v>
+      </c>
+      <c r="M39" t="n">
+        <v>-24.443485</v>
+      </c>
+      <c r="N39" t="n">
+        <v>-42.508705</v>
+      </c>
+      <c r="Q39" s="7" t="n">
+        <v>46298.59305555555</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-10-05 11:51</t>
+        </is>
+      </c>
+      <c r="M40" t="n">
+        <v>-24.603739</v>
+      </c>
+      <c r="N40" t="n">
+        <v>-42.447128</v>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>2026-10-04 21:51</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:23</t>
+        </is>
+      </c>
+      <c r="M41" t="n">
+        <v>-24.603739</v>
+      </c>
+      <c r="N41" t="n">
+        <v>-42.447128</v>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>2026-10-04 21:51</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-10-08 08:36</t>
+        </is>
+      </c>
+      <c r="M42" t="n">
+        <v>-24.447128</v>
+      </c>
+      <c r="N42" t="n">
+        <v>-42.447128</v>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>2026-10-04 21:51</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-10-12 10:22</t>
+        </is>
+      </c>
+      <c r="M43" t="n">
+        <v>-24.708138</v>
+      </c>
+      <c r="N43" t="n">
+        <v>-42.431637</v>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>2026-10-12 07:57</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-10-13 05:59</t>
+        </is>
+      </c>
+      <c r="M44" t="n">
+        <v>-24.708138</v>
+      </c>
+      <c r="N44" t="n">
+        <v>-42.431637</v>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>2026-10-12 07:57</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-10-14 14:10</t>
+        </is>
+      </c>
+      <c r="M45" t="n">
+        <v>-23.178743</v>
+      </c>
+      <c r="N45" t="n">
+        <v>-43.049114</v>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>2026-10-14 14:06</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-10-14 15:06</t>
+        </is>
+      </c>
+      <c r="M46" t="n">
+        <v>-23.041821</v>
+      </c>
+      <c r="N46" t="n">
+        <v>-43.104267</v>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>2026-10-14 15:00</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-10-15 07:21</t>
+        </is>
+      </c>
+      <c r="M47" t="n">
+        <v>-22.881216</v>
+      </c>
+      <c r="N47" t="n">
+        <v>-43.116375</v>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>2026-10-15 07:16</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-10-15 10:08</t>
+        </is>
+      </c>
+      <c r="M48" t="n">
+        <v>-22.881237</v>
+      </c>
+      <c r="N48" t="n">
+        <v>-43.11636</v>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>2026-10-15 10:07</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-10-18 09:38</t>
+        </is>
+      </c>
+      <c r="M49" t="n">
+        <v>-22.893696</v>
+      </c>
+      <c r="N49" t="n">
+        <v>-43.212658</v>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>2026-10-18 09:33</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-10-18 14:49</t>
+        </is>
+      </c>
+      <c r="M50" t="n">
+        <v>-23.364546</v>
+      </c>
+      <c r="N50" t="n">
+        <v>-42.978527</v>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>2026-10-18 14:47</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:41</t>
+        </is>
+      </c>
+      <c r="M51" t="n">
+        <v>-22.84469</v>
+      </c>
+      <c r="N51" t="n">
+        <v>-43.141312</v>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:33</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
         </is>
       </c>
     </row>
@@ -8505,7 +12927,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S23"/>
+  <dimension ref="A1:S52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="26" customWidth="1" style="8" min="1" max="1"/>
@@ -9057,7 +13479,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="12" t="n">
+      <c r="A22" s="7" t="n">
         <v>46278.85416666666</v>
       </c>
       <c r="M22" t="n">
@@ -9066,7 +13488,7 @@
       <c r="N22" t="n">
         <v>-42.720772</v>
       </c>
-      <c r="Q22" s="12" t="n">
+      <c r="Q22" s="7" t="n">
         <v>46278.36527777778</v>
       </c>
       <c r="S22" t="inlineStr">
@@ -9076,7 +13498,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="n">
+      <c r="A23" s="7" t="n">
         <v>46279.73333333333</v>
       </c>
       <c r="M23" t="n">
@@ -9085,12 +13507,615 @@
       <c r="N23" t="n">
         <v>-42.720772</v>
       </c>
-      <c r="Q23" s="12" t="n">
+      <c r="Q23" s="7" t="n">
         <v>46278.36527777778</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
           <t>Stopped</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="n">
+        <v>46280.53125</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-22.886568</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-43.156555</v>
+      </c>
+      <c r="Q24" s="7" t="n">
+        <v>46280.52986111111</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="n">
+        <v>46281.53472222222</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-22.85301</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-43.144794</v>
+      </c>
+      <c r="Q25" s="7" t="n">
+        <v>46281.52986111111</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="n">
+        <v>46281.62083333333</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-22.851679</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-43.14489</v>
+      </c>
+      <c r="Q26" s="7" t="n">
+        <v>46281.61736111111</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="n">
+        <v>46283.75694444445</v>
+      </c>
+      <c r="M27" t="n">
+        <v>-24.086216</v>
+      </c>
+      <c r="N27" t="n">
+        <v>-44.073032</v>
+      </c>
+      <c r="Q27" s="7" t="n">
+        <v>46283.27777777778</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="n">
+        <v>46287.35763888889</v>
+      </c>
+      <c r="M28" t="n">
+        <v>-24.355833</v>
+      </c>
+      <c r="N28" t="n">
+        <v>-44.385132</v>
+      </c>
+      <c r="Q28" s="7" t="n">
+        <v>46287.32986111111</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="n">
+        <v>46287.71666666667</v>
+      </c>
+      <c r="M29" t="n">
+        <v>-24.353418</v>
+      </c>
+      <c r="N29" t="n">
+        <v>-44.383606</v>
+      </c>
+      <c r="Q29" s="7" t="n">
+        <v>46287.36527777778</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="n">
+        <v>46288.26597222222</v>
+      </c>
+      <c r="M30" t="n">
+        <v>-24.625029</v>
+      </c>
+      <c r="N30" t="n">
+        <v>-43.25388</v>
+      </c>
+      <c r="Q30" s="7" t="n">
+        <v>46288.10902777778</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="n">
+        <v>46290.46666666667</v>
+      </c>
+      <c r="M31" t="n">
+        <v>-24.625029</v>
+      </c>
+      <c r="N31" t="n">
+        <v>-43.25388</v>
+      </c>
+      <c r="Q31" s="7" t="n">
+        <v>46288.10902777778</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="n">
+        <v>46291.32291666666</v>
+      </c>
+      <c r="M32" t="n">
+        <v>-24.625029</v>
+      </c>
+      <c r="N32" t="n">
+        <v>-43.25388</v>
+      </c>
+      <c r="Q32" s="7" t="n">
+        <v>46288.10902777778</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="n">
+        <v>46295.34652777778</v>
+      </c>
+      <c r="M33" t="n">
+        <v>-22.85214</v>
+      </c>
+      <c r="N33" t="n">
+        <v>-43.136295</v>
+      </c>
+      <c r="Q33" s="7" t="n">
+        <v>46295.34375</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="n">
+        <v>46296.35902777778</v>
+      </c>
+      <c r="M34" t="n">
+        <v>-22.853456</v>
+      </c>
+      <c r="N34" t="n">
+        <v>-43.134872</v>
+      </c>
+      <c r="Q34" s="7" t="n">
+        <v>46296.35694444444</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="n">
+        <v>46296.53263888889</v>
+      </c>
+      <c r="M35" t="n">
+        <v>-22.852791</v>
+      </c>
+      <c r="N35" t="n">
+        <v>-43.134754</v>
+      </c>
+      <c r="Q35" s="7" t="n">
+        <v>46296.52986111111</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="n">
+        <v>46296.65833333333</v>
+      </c>
+      <c r="M36" t="n">
+        <v>-22.852755</v>
+      </c>
+      <c r="N36" t="n">
+        <v>-43.134693</v>
+      </c>
+      <c r="Q36" s="7" t="n">
+        <v>46296.64861111111</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="n">
+        <v>46297.45625</v>
+      </c>
+      <c r="M37" t="n">
+        <v>-22.852737</v>
+      </c>
+      <c r="N37" t="n">
+        <v>-43.134815</v>
+      </c>
+      <c r="Q37" s="7" t="n">
+        <v>46297.45486111111</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="n">
+        <v>46298.43402777778</v>
+      </c>
+      <c r="M38" t="n">
+        <v>-22.891071</v>
+      </c>
+      <c r="N38" t="n">
+        <v>-43.213928</v>
+      </c>
+      <c r="Q38" s="7" t="n">
+        <v>46298.43333333333</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="n">
+        <v>46298.88194444445</v>
+      </c>
+      <c r="M39" t="n">
+        <v>-23.033554</v>
+      </c>
+      <c r="N39" t="n">
+        <v>-43.073128</v>
+      </c>
+      <c r="Q39" s="7" t="n">
+        <v>46298.87916666667</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-10-05 11:51</t>
+        </is>
+      </c>
+      <c r="M40" t="n">
+        <v>-23.96896</v>
+      </c>
+      <c r="N40" t="n">
+        <v>-43.950153</v>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>2026-10-05 07:14</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:23</t>
+        </is>
+      </c>
+      <c r="M41" t="n">
+        <v>-24.352686</v>
+      </c>
+      <c r="N41" t="n">
+        <v>-44.383675</v>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>2026-10-06 09:49</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-10-08 08:36</t>
+        </is>
+      </c>
+      <c r="M42" t="n">
+        <v>-24.488968</v>
+      </c>
+      <c r="N42" t="n">
+        <v>-42.736382</v>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>2026-10-08 05:21</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-10-12 10:22</t>
+        </is>
+      </c>
+      <c r="M43" t="n">
+        <v>-22.893711</v>
+      </c>
+      <c r="N43" t="n">
+        <v>-43.21262</v>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>2026-10-12 10:14</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-10-12 14:32</t>
+        </is>
+      </c>
+      <c r="M44" t="n">
+        <v>-22.893671</v>
+      </c>
+      <c r="N44" t="n">
+        <v>-43.212681</v>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>2026-10-12 14:26</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>Moored</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-10-13 05:59</t>
+        </is>
+      </c>
+      <c r="M45" t="n">
+        <v>-23.215876</v>
+      </c>
+      <c r="N45" t="n">
+        <v>-43.065735</v>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>2026-10-13 05:24</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-10-13 09:26</t>
+        </is>
+      </c>
+      <c r="M46" t="n">
+        <v>-23.360332</v>
+      </c>
+      <c r="N46" t="n">
+        <v>-43.028786</v>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>2026-10-13 06:21</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-10-14 14:10</t>
+        </is>
+      </c>
+      <c r="M47" t="n">
+        <v>-24.352678</v>
+      </c>
+      <c r="N47" t="n">
+        <v>-44.383419</v>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>2026-10-14 13:29</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-10-14 15:06</t>
+        </is>
+      </c>
+      <c r="M48" t="n">
+        <v>-24.352718</v>
+      </c>
+      <c r="N48" t="n">
+        <v>-44.38332</v>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>2026-10-14 14:54</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-10-15 07:21</t>
+        </is>
+      </c>
+      <c r="M49" t="n">
+        <v>-25.149796</v>
+      </c>
+      <c r="N49" t="n">
+        <v>-45.133465</v>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>2026-10-15 00:23</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-10-18 09:38</t>
+        </is>
+      </c>
+      <c r="M50" t="n">
+        <v>-24.300486</v>
+      </c>
+      <c r="N50" t="n">
+        <v>-42.716259</v>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>2026-10-17 21:01</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-10-18 14:49</t>
+        </is>
+      </c>
+      <c r="M51" t="n">
+        <v>-24.308268</v>
+      </c>
+      <c r="N51" t="n">
+        <v>-42.715923</v>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>2026-10-18 14:34</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:41</t>
+        </is>
+      </c>
+      <c r="M52" t="n">
+        <v>-23.851385</v>
+      </c>
+      <c r="N52" t="n">
+        <v>-43.874901</v>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>2026-10-23 06:14</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
         </is>
       </c>
     </row>
@@ -9106,7 +14131,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S24"/>
+  <dimension ref="A1:S52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="11.33203125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -9742,7 +14767,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="n">
+      <c r="A23" s="7" t="n">
         <v>46278.85416666666</v>
       </c>
       <c r="M23" t="n">
@@ -9751,7 +14776,7 @@
       <c r="N23" t="n">
         <v>-42.475761</v>
       </c>
-      <c r="Q23" s="12" t="n">
+      <c r="Q23" s="7" t="n">
         <v>46278.47986111111</v>
       </c>
       <c r="S23" t="inlineStr">
@@ -9761,7 +14786,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="12" t="n">
+      <c r="A24" s="7" t="n">
         <v>46279.73333333333</v>
       </c>
       <c r="M24" t="n">
@@ -9770,12 +14795,596 @@
       <c r="N24" t="n">
         <v>-42.475761</v>
       </c>
-      <c r="Q24" s="12" t="n">
+      <c r="Q24" s="7" t="n">
         <v>46278.47986111111</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
           <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="n">
+        <v>46280.53125</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-22.844574</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-43.147038</v>
+      </c>
+      <c r="Q25" s="7" t="n">
+        <v>46280.52916666667</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="n">
+        <v>46281.53472222222</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-22.845257</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-43.147293</v>
+      </c>
+      <c r="Q26" s="7" t="n">
+        <v>46281.52916666667</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="n">
+        <v>46281.62083333333</v>
+      </c>
+      <c r="M27" t="n">
+        <v>-22.844372</v>
+      </c>
+      <c r="N27" t="n">
+        <v>-43.147114</v>
+      </c>
+      <c r="Q27" s="7" t="n">
+        <v>46281.61666666667</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="n">
+        <v>46283.75694444445</v>
+      </c>
+      <c r="M28" t="n">
+        <v>-22.844227</v>
+      </c>
+      <c r="N28" t="n">
+        <v>-43.1478</v>
+      </c>
+      <c r="Q28" s="7" t="n">
+        <v>46283.75486111111</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="n">
+        <v>46287.35763888889</v>
+      </c>
+      <c r="M29" t="n">
+        <v>-24.759748</v>
+      </c>
+      <c r="N29" t="n">
+        <v>-42.465107</v>
+      </c>
+      <c r="Q29" s="7" t="n">
+        <v>46287.16875</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="n">
+        <v>46288.26597222222</v>
+      </c>
+      <c r="M30" t="n">
+        <v>-24.542902</v>
+      </c>
+      <c r="N30" t="n">
+        <v>-42.470768</v>
+      </c>
+      <c r="Q30" s="7" t="n">
+        <v>46288.26458333333</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="n">
+        <v>46290.46666666667</v>
+      </c>
+      <c r="M31" t="n">
+        <v>-24.542902</v>
+      </c>
+      <c r="N31" t="n">
+        <v>-42.470768</v>
+      </c>
+      <c r="Q31" s="7" t="n">
+        <v>46288.26458333333</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>Stopped</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="n">
+        <v>46291.32291666666</v>
+      </c>
+      <c r="M32" t="n">
+        <v>-22.845289</v>
+      </c>
+      <c r="N32" t="n">
+        <v>-43.138329</v>
+      </c>
+      <c r="Q32" s="7" t="n">
+        <v>46291.32291666666</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="n">
+        <v>46295.34652777778</v>
+      </c>
+      <c r="M33" t="n">
+        <v>-22.840258</v>
+      </c>
+      <c r="N33" t="n">
+        <v>-43.135273</v>
+      </c>
+      <c r="Q33" s="7" t="n">
+        <v>46295.34375</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="n">
+        <v>46296.35902777778</v>
+      </c>
+      <c r="M34" t="n">
+        <v>-22.840363</v>
+      </c>
+      <c r="N34" t="n">
+        <v>-43.135223</v>
+      </c>
+      <c r="Q34" s="7" t="n">
+        <v>46296.35763888889</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="n">
+        <v>46296.53263888889</v>
+      </c>
+      <c r="M35" t="n">
+        <v>-22.839912</v>
+      </c>
+      <c r="N35" t="n">
+        <v>-43.13541</v>
+      </c>
+      <c r="Q35" s="7" t="n">
+        <v>46296.53055555555</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="n">
+        <v>46296.65833333333</v>
+      </c>
+      <c r="M36" t="n">
+        <v>-22.839415</v>
+      </c>
+      <c r="N36" t="n">
+        <v>-43.134964</v>
+      </c>
+      <c r="Q36" s="7" t="n">
+        <v>46296.65347222222</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="n">
+        <v>46297.45625</v>
+      </c>
+      <c r="M37" t="n">
+        <v>-22.839447</v>
+      </c>
+      <c r="N37" t="n">
+        <v>-43.135139</v>
+      </c>
+      <c r="Q37" s="7" t="n">
+        <v>46297.45347222222</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="n">
+        <v>46298.43402777778</v>
+      </c>
+      <c r="M38" t="n">
+        <v>-22.839849</v>
+      </c>
+      <c r="N38" t="n">
+        <v>-43.135548</v>
+      </c>
+      <c r="Q38" s="7" t="n">
+        <v>46298.43263888889</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="n">
+        <v>46298.88194444445</v>
+      </c>
+      <c r="M39" t="n">
+        <v>-22.91136</v>
+      </c>
+      <c r="N39" t="n">
+        <v>-43.148304</v>
+      </c>
+      <c r="Q39" s="7" t="n">
+        <v>46298.87986111111</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-10-05 11:51</t>
+        </is>
+      </c>
+      <c r="M40" t="n">
+        <v>-24.623295</v>
+      </c>
+      <c r="N40" t="n">
+        <v>-42.461613</v>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>2026-10-05 01:15</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:23</t>
+        </is>
+      </c>
+      <c r="M41" t="n">
+        <v>-22.838383</v>
+      </c>
+      <c r="N41" t="n">
+        <v>-43.137455</v>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>2026-10-06 11:19</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-10-08 08:36</t>
+        </is>
+      </c>
+      <c r="M42" t="n">
+        <v>-23.481831</v>
+      </c>
+      <c r="N42" t="n">
+        <v>-42.875214</v>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>2026-10-08 08:14</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-10-12 10:22</t>
+        </is>
+      </c>
+      <c r="M43" t="n">
+        <v>-22.844959</v>
+      </c>
+      <c r="N43" t="n">
+        <v>-43.148888</v>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>2026-10-12 10:17</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-10-12 14:32</t>
+        </is>
+      </c>
+      <c r="M44" t="n">
+        <v>-22.844112</v>
+      </c>
+      <c r="N44" t="n">
+        <v>-43.148628</v>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>2026-10-12 14:29</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-10-13 05:59</t>
+        </is>
+      </c>
+      <c r="M45" t="n">
+        <v>-22.845165</v>
+      </c>
+      <c r="N45" t="n">
+        <v>-43.14843</v>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>2026-10-13 05:56</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-10-13 09:26</t>
+        </is>
+      </c>
+      <c r="M46" t="n">
+        <v>-22.844994</v>
+      </c>
+      <c r="N46" t="n">
+        <v>-43.148685</v>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>2026-10-13 09:17</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-10-14 14:10</t>
+        </is>
+      </c>
+      <c r="M47" t="n">
+        <v>-22.844179</v>
+      </c>
+      <c r="N47" t="n">
+        <v>-43.148479</v>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>2026-10-14 14:05</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-10-14 15:06</t>
+        </is>
+      </c>
+      <c r="M48" t="n">
+        <v>-22.844097</v>
+      </c>
+      <c r="N48" t="n">
+        <v>-43.148499</v>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>2026-10-14 14:59</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-10-15 07:21</t>
+        </is>
+      </c>
+      <c r="M49" t="n">
+        <v>-23.47624</v>
+      </c>
+      <c r="N49" t="n">
+        <v>-42.924694</v>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>2026-10-14 22:06</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>Underway using Engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-10-18 09:38</t>
+        </is>
+      </c>
+      <c r="M50" t="n">
+        <v>-22.846895</v>
+      </c>
+      <c r="N50" t="n">
+        <v>-43.148674</v>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>2026-10-18 09:32</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-10-18 14:49</t>
+        </is>
+      </c>
+      <c r="M51" t="n">
+        <v>-22.846186</v>
+      </c>
+      <c r="N51" t="n">
+        <v>-43.148586</v>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>2026-10-18 14:44</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>At Anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-10-23 11:41</t>
+        </is>
+      </c>
+      <c r="M52" t="n">
+        <v>-24.542931</v>
+      </c>
+      <c r="N52" t="n">
+        <v>-42.470837</v>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>2026-10-23 04:21</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>Restricted Manoeuvrability</t>
         </is>
       </c>
     </row>
